--- a/stores_base.xlsx
+++ b/stores_base.xlsx
@@ -49,7 +49,7 @@
     <t>经度</t>
   </si>
   <si>
-    <t>维度</t>
+    <t>纬度</t>
   </si>
   <si>
     <t>慢慢山茶咖馆</t>
